--- a/tasks/finalpool/fetch-arxiv-citation-network-excel-notion/groundtruth_workspace/Citation_Network_Report.xlsx
+++ b/tasks/finalpool/fetch-arxiv-citation-network-excel-notion/groundtruth_workspace/Citation_Network_Report.xlsx
@@ -429,31 +429,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Paper_ID</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Citations</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Relevance_Score</t>
         </is>
@@ -462,92 +452,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301.01234</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Scaling Laws for LLMs</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>LLMs</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="B2" t="n">
         <v>450</v>
       </c>
-      <c r="E2" t="n">
+      <c r="C2" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2302.05678</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vision Transformer Advances</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="B3" t="n">
         <v>320</v>
       </c>
-      <c r="E3" t="n">
+      <c r="C3" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303.09012</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Multi-Agent RL Framework</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="B4" t="n">
         <v>180</v>
       </c>
-      <c r="E4" t="n">
+      <c r="C4" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2304.03456</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Federated Learning Survey</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="B5" t="n">
         <v>250</v>
       </c>
-      <c r="E5" t="n">
+      <c r="C5" t="n">
         <v>68</v>
       </c>
     </row>
@@ -630,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,11 +594,6 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -659,11 +604,6 @@
           <t>Deep dive review</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LLMs</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -672,11 +612,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Literature survey</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CV</t>
         </is>
       </c>
     </row>
